--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,6 +1436,137 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127707039</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58492</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ramsjöhultsskogen Majbron, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574315</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6538835</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>7 olika Vanlig Padda hoppade på vägen runt Majbron när vi passerade förbi där vid 21:30-tiden. Olika storlekar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cathrin Lindström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cathrin Lindström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>127707039</v>
       </c>
       <c r="B8" t="n">
-        <v>58492</v>
+        <v>58494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1567,6 +1567,137 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127707086</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58524</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100117</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Långbensgroda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana dalmatina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ramsjöhultsskogen Majbron, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574315</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6538835</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långbensgroda hoppade på vägen vid Majbron, Ramsjöhultsskogen vid 21:30-tiden när vi gick förbi där.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cathrin Lindström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cathrin Lindström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>127707039</v>
       </c>
       <c r="B8" t="n">
-        <v>58494</v>
+        <v>58497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>127707039</v>
       </c>
       <c r="B8" t="n">
-        <v>58497</v>
+        <v>58503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58524</v>
+        <v>58530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>127707039</v>
       </c>
       <c r="B8" t="n">
-        <v>58503</v>
+        <v>58504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58530</v>
+        <v>58531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>127707039</v>
       </c>
       <c r="B8" t="n">
-        <v>58504</v>
+        <v>58515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58531</v>
+        <v>58543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58543</v>
+        <v>58547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58547</v>
+        <v>58578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1572,29 +1572,29 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58578</v>
+        <v>58580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100117</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1602,11 +1602,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1677,6 +1680,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58580</v>
+        <v>58582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>127707086</v>
       </c>
       <c r="B9" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5034933</v>
+        <v>734558</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574350.7982079531</v>
+        <v>574351</v>
       </c>
       <c r="R2" t="n">
-        <v>6538582.224537291</v>
+        <v>6538582</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -762,24 +752,14 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>5 blommande plantor</t>
+          <t>på block</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>fd torp m omg</t>
+          <t>fd torp m omg.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>734558</v>
+        <v>1169508</v>
       </c>
       <c r="B3" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,31 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -860,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574350.7982079531</v>
+        <v>574351</v>
       </c>
       <c r="R3" t="n">
-        <v>6538582.224537291</v>
+        <v>6538582</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -893,24 +868,9 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på block</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1169508</v>
+        <v>13451718</v>
       </c>
       <c r="B4" t="n">
-        <v>89939</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,43 +913,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>101377</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skirtorp 1750 m nö, Srm</t>
+          <t>Stensjötorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574350.7982079531</v>
+        <v>574371</v>
       </c>
       <c r="R4" t="n">
-        <v>6538582.224537291</v>
+        <v>6538582</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1021,22 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,11 +993,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>fd torp m omg.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1068,59 +1009,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5742693</v>
+        <v>13451716</v>
       </c>
       <c r="B5" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skirtorp 1750 m nö, Srm</t>
+          <t>Stensjötorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574350.7982079531</v>
+        <v>574371</v>
       </c>
       <c r="R5" t="n">
-        <v>6538582.224537291</v>
+        <v>6538582</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1147,22 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,11 +1100,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>fd torp m omg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1194,15 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13451718</v>
+        <v>127707039</v>
       </c>
       <c r="B6" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,27 +1127,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101377</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1240,17 +1161,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stensjötorp, Srm</t>
+          <t>Ramsjöhultsskogen Majbron, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574370.9452632521</v>
+        <v>574315</v>
       </c>
       <c r="R6" t="n">
-        <v>6538582.098824522</v>
+        <v>6538835</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,22 +1195,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2008-02-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2008-02-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 olika Vanlig Padda hoppade på vägen runt Majbron när vi passerade förbi där vid 21:30-tiden. Olika storlekar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,31 +1226,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13451716</v>
+        <v>127707086</v>
       </c>
       <c r="B7" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,29 +1258,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1362,17 +1295,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensjötorp, Srm</t>
+          <t>Ramsjöhultsskogen Majbron, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574370.9452632521</v>
+        <v>574315</v>
       </c>
       <c r="R7" t="n">
-        <v>6538582.098824522</v>
+        <v>6538835</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,22 +1329,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-02-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-02-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långbensgroda hoppade på vägen vid Majbron, Ramsjöhultsskogen vid 21:30-tiden när vi gick förbi där.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,28 +1358,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127707039</v>
+        <v>5034933</v>
       </c>
       <c r="B8" t="n">
-        <v>58515</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,51 +1393,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ramsjöhultsskogen Majbron, Srm</t>
+          <t>Skirtorp 1750 m nö, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574315</v>
+        <v>574351</v>
       </c>
       <c r="R8" t="n">
-        <v>6538835</v>
+        <v>6538582</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,27 +1461,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21:35</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>21:35</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>7 olika Vanlig Padda hoppade på vägen runt Majbron när vi passerade förbi där vid 21:30-tiden. Olika storlekar.</t>
+          <t>5 blommande plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,52 +1483,52 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Bäck</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>fd torp m omg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cathrin Lindström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cathrin Lindström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127707086</v>
+        <v>5742693</v>
       </c>
       <c r="B9" t="n">
-        <v>58584</v>
+        <v>103403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208250</v>
+        <v>223246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1602,32 +1536,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ramsjöhultsskogen Majbron, Srm</t>
+          <t>Skirtorp 1750 m nö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574315</v>
+        <v>574351</v>
       </c>
       <c r="R9" t="n">
-        <v>6538835</v>
+        <v>6538582</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1651,27 +1577,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>21:35</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långbensgroda hoppade på vägen vid Majbron, Ramsjöhultsskogen vid 21:30-tiden när vi gick förbi där.</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,24 +1591,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Bäck</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>fd torp m omg</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cathrin Lindström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cathrin Lindström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/734558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1169508</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13451718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13451716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127707039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127707086</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5034933</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1611,8 +1651,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5742693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5034933</v>
+        <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>101326</v>
+        <v>99186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1460,19 +1460,25 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skirtorp 1750 m nö, Srm</t>
+          <t>Vägen mellan Stensjöstugan och Kolugnen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574351</v>
+        <v>574491</v>
       </c>
       <c r="R8" t="n">
-        <v>6538582</v>
+        <v>6538206</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,17 +1502,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 blommande plantor</t>
+          <t>Massor med orkidéer, Fläcknycklar växer i dikena mellan Stensjöstugan och Kolugnen i Ramsjöhultsskogen sedda av Monica Linde’</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,70 +1521,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>fd torp m omg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5034933</t>
+          <t>https://artportalen.se/Sighting/135684839</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5742693</v>
+        <v>5034933</v>
       </c>
       <c r="B9" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1625,6 +1632,11 @@
           <t>2008-02-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 blommande plantor</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1652,6 +1664,122 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5034933</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5742693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skirtorp 1750 m nö, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574351</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6538582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>fd torp m omg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5742693</t>
         </is>
@@ -1667,6 +1795,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5034933</v>
+        <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>101326</v>
+        <v>99191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1460,19 +1460,25 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skirtorp 1750 m nö, Srm</t>
+          <t>Vägen mellan Stensjöstugan och Kolugnen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574351</v>
+        <v>574491</v>
       </c>
       <c r="R8" t="n">
-        <v>6538582</v>
+        <v>6538206</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,17 +1502,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 blommande plantor</t>
+          <t>Massor med orkidéer, Fläcknycklar växer i dikena mellan Stensjöstugan och Kolugnen i Ramsjöhultsskogen sedda av Monica Linde’</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,70 +1521,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>fd torp m omg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Cathrin Lindström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5034933</t>
+          <t>https://artportalen.se/Sighting/135684839</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5742693</v>
+        <v>5034933</v>
       </c>
       <c r="B9" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1625,6 +1632,11 @@
           <t>2008-02-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 blommande plantor</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1652,6 +1664,122 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5034933</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5742693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skirtorp 1750 m nö, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574351</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6538582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>fd torp m omg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5742693</t>
         </is>
@@ -1667,6 +1795,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54002-2022 artfynd.xlsx
+++ b/artfynd/A 54002-2022 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>135684839</v>
       </c>
       <c r="B8" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
